--- a/CURRENT MONTH GST WORKINGS/WORKINGS/GST WORKING_BEEJAL INFRA_AUGUST 2026.xlsx
+++ b/CURRENT MONTH GST WORKINGS/WORKINGS/GST WORKING_BEEJAL INFRA_AUGUST 2026.xlsx
@@ -8,9 +8,14 @@
   <sheets>
     <sheet name="SALES" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="PURCHASES" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="PURCHASES1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="PURCHASES2" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="PURCHASES3" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="PURCHASES4" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="PURCHASES5" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId3"/>
+    <externalReference r:id="rId8"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'SALES'!$A$1:$O$19</definedName>
@@ -169,7 +174,7 @@
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -444,6 +449,7 @@
     <xf numFmtId="43" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1529,4 +1535,1183 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SR. NO.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>INVOICE NO.</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>PARTY NAME</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>GST NO.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>NET AMOUNT</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>CGST</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>SGST</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>IGST</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>R/OFF</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>TOTAL AMOUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Invoice Details</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SR. NO.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>INVOICE NO.</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>PARTY NAME</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>GST NO.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>NET AMOUNT</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>CGST</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>SGST</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>IGST</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>R/OFF</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>TOTAL AMOUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AUGUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SALA/26-27/143</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>08/08/2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SHREE ANSUYA LEATHER ARTS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>27AHMPP0142M1Z2</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>5814.75</v>
+      </c>
+      <c r="H3" t="n">
+        <v>238.63</v>
+      </c>
+      <c r="J3" t="n">
+        <v>238.63</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" t="n">
+        <v>6292</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>26-27/00442</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AMIT HARDWARE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>27AXQPA4425N1Z4</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>720</v>
+      </c>
+      <c r="J4" t="n">
+        <v>720</v>
+      </c>
+      <c r="N4" t="n">
+        <v>9440</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>26-27/00470</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AMIT HARDWARE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>27AXQPA4425N1Z4</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>19450</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1750.5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1750.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>22951</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CRN364441664721</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Porter</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>27AAGCR8772D1Z2</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>486</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="J6" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="N6" t="n">
+        <v>510.3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CRN364441664721</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Porter</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>27AAGCR8772D1Z2</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>486</v>
+      </c>
+      <c r="L7" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="N7" t="n">
+        <v>510.3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SR. NO.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>INVOICE NO.</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>PARTY NAME</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>GST NO.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>NET AMOUNT</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>CGST</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>SGST</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>IGST</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>R/OFF</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>TOTAL AMOUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AUGUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SALA/26-27/143</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>08/08/2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SHREE ANSUYA LEATHER ARTS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>27AHMPP0142M1Z2</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>5814.75</v>
+      </c>
+      <c r="H3" t="n">
+        <v>238.63</v>
+      </c>
+      <c r="J3" t="n">
+        <v>238.63</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-0.009999999999990905</v>
+      </c>
+      <c r="N3" t="n">
+        <v>6292</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>26-27/00442</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AMIT HARDWARE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>27AXQPA4425N1Z4</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>720</v>
+      </c>
+      <c r="J4" t="n">
+        <v>720</v>
+      </c>
+      <c r="N4" t="n">
+        <v>9440</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>26-27/00470</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AMIT HARDWARE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>27AXQPA4425N1Z4</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>19450</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1750.5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1750.5</v>
+      </c>
+      <c r="N5" t="n">
+        <v>22951</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CRN364441664721</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Porter</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>27AAGCR8772D1Z2</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>486</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="J6" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.06581410364015e-14</v>
+      </c>
+      <c r="N6" t="n">
+        <v>510.3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CRN364441664721</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Porter</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>27AAGCR8772D1Z2</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>486</v>
+      </c>
+      <c r="L7" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.06581410364015e-14</v>
+      </c>
+      <c r="N7" t="n">
+        <v>510.3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SR. NO.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>INVOICE NO.</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>PARTY NAME</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>GST NO.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>NET AMOUNT</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>CGST</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>SGST</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>IGST</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>R/OFF</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>TOTAL AMOUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AUGUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SALA/26-27/143</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>08/08/2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SHREE ANSUYA LEATHER ARTS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>27AHMPP0142M1Z2</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>5814.75</v>
+      </c>
+      <c r="H3" t="n">
+        <v>238.63</v>
+      </c>
+      <c r="J3" t="n">
+        <v>238.63</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-0.009999999999990905</v>
+      </c>
+      <c r="N3" t="n">
+        <v>6292</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>26-27/00442</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AMIT HARDWARE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>27AXQPA4425N1Z4</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>720</v>
+      </c>
+      <c r="J4" t="n">
+        <v>720</v>
+      </c>
+      <c r="N4" t="n">
+        <v>9440</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>26-27/00470</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AMIT HARDWARE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>27AXQPA4425N1Z4</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>19450</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1750.5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1750.5</v>
+      </c>
+      <c r="N5" t="n">
+        <v>22951</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CRN364441664721</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Porter</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>27AAGCR8772D1Z2</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>486</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="J6" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.06581410364015e-14</v>
+      </c>
+      <c r="N6" t="n">
+        <v>510.3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CRN364441664721</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Porter</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>27AAGCR8772D1Z2</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>486</v>
+      </c>
+      <c r="L7" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.06581410364015e-14</v>
+      </c>
+      <c r="N7" t="n">
+        <v>510.3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SR. NO.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>INVOICE NO.</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>PARTY NAME</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>GST NO.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>NET AMOUNT</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>CGST</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>SGST</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>IGST</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>R/OFF</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>TOTAL AMOUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AUGUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SALA/26-27/143</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>08/08/2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SHREE ANSUYA LEATHER ARTS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>27AHMPP0142M1Z2</t>
+        </is>
+      </c>
+      <c r="F3" s="92" t="n">
+        <v>5814.75</v>
+      </c>
+      <c r="H3" s="92" t="n">
+        <v>238.63</v>
+      </c>
+      <c r="J3" s="92" t="n">
+        <v>238.63</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" s="92" t="n">
+        <v>-0.009999999999990905</v>
+      </c>
+      <c r="N3" s="92" t="n">
+        <v>6292</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>26-27/00442</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AMIT HARDWARE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>27AXQPA4425N1Z4</t>
+        </is>
+      </c>
+      <c r="F4" s="92" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H4" s="92" t="n">
+        <v>720</v>
+      </c>
+      <c r="J4" s="92" t="n">
+        <v>720</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" s="92" t="n">
+        <v>9440</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>26-27/00470</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AMIT HARDWARE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>27AXQPA4425N1Z4</t>
+        </is>
+      </c>
+      <c r="F5" s="92" t="n">
+        <v>19450</v>
+      </c>
+      <c r="H5" s="92" t="n">
+        <v>1750.5</v>
+      </c>
+      <c r="J5" s="92" t="n">
+        <v>1750.5</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" s="92" t="n">
+        <v>22951</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CRN364441664721</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Porter</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>27AAGCR8772D1Z2</t>
+        </is>
+      </c>
+      <c r="F6" s="92" t="n">
+        <v>486</v>
+      </c>
+      <c r="H6" s="92" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="J6" s="92" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" s="92" t="n">
+        <v>1.06581410364015e-14</v>
+      </c>
+      <c r="N6" s="92" t="n">
+        <v>510.3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CRN364441664721</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Porter</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>27AAGCR8772D1Z2</t>
+        </is>
+      </c>
+      <c r="F7" s="92" t="n">
+        <v>486</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="L7" s="92" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="M7" s="92" t="n">
+        <v>1.06581410364015e-14</v>
+      </c>
+      <c r="N7" s="92" t="n">
+        <v>510.3</v>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/CURRENT MONTH GST WORKINGS/WORKINGS/GST WORKING_BEEJAL INFRA_AUGUST 2026.xlsx
+++ b/CURRENT MONTH GST WORKINGS/WORKINGS/GST WORKING_BEEJAL INFRA_AUGUST 2026.xlsx
@@ -13,9 +13,14 @@
     <sheet name="PURCHASES3" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="PURCHASES4" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="PURCHASES5" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="PURCHASES6" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="PURCHASES7" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="PURCHASES8" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="PURCHASES9" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="PURCHASES10" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId8"/>
+    <externalReference r:id="rId13"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'SALES'!$A$1:$O$19</definedName>
@@ -1516,6 +1521,835 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SR. NO.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>INVOICE NO.</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>PARTY NAME</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>GST NO.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>NET AMOUNT</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>CGST</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>SGST</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>IGST</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>R/OFF</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>TOTAL AMOUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AUGUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SALA/26-27/143</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>08/08/2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SHREE ANSUYA LEATHER ARTS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>27AHMPP0142M1Z2</t>
+        </is>
+      </c>
+      <c r="F3" s="92" t="n">
+        <v>5814.75</v>
+      </c>
+      <c r="H3" s="92" t="n">
+        <v>238.63</v>
+      </c>
+      <c r="J3" s="92" t="n">
+        <v>238.63</v>
+      </c>
+      <c r="M3" s="92" t="n">
+        <v>-0.009999999999990905</v>
+      </c>
+      <c r="N3" s="92" t="n">
+        <v>6292</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>26-27/00442</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AMIT HARDWARE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>27AXQPA4425N1Z4</t>
+        </is>
+      </c>
+      <c r="F4" s="92" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H4" s="92" t="n">
+        <v>720</v>
+      </c>
+      <c r="J4" s="92" t="n">
+        <v>720</v>
+      </c>
+      <c r="N4" s="92" t="n">
+        <v>9440</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>26-27/00470</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AMIT HARDWARE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>27AXQPA4425N1Z4</t>
+        </is>
+      </c>
+      <c r="F5" s="92" t="n">
+        <v>19450</v>
+      </c>
+      <c r="H5" s="92" t="n">
+        <v>1750.5</v>
+      </c>
+      <c r="J5" s="92" t="n">
+        <v>1750.5</v>
+      </c>
+      <c r="N5" s="92" t="n">
+        <v>22951</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CRN364441664721</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Porter</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>27AAGCR8772D1Z2</t>
+        </is>
+      </c>
+      <c r="F6" s="92" t="n">
+        <v>486</v>
+      </c>
+      <c r="H6" s="92" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="J6" s="92" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="M6" s="92" t="n">
+        <v>1.06581410364015e-14</v>
+      </c>
+      <c r="N6" s="92" t="n">
+        <v>510.3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CRN364441664721</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Porter</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>27AAGCR8772D1Z2</t>
+        </is>
+      </c>
+      <c r="F7" s="92" t="n">
+        <v>486</v>
+      </c>
+      <c r="L7" s="92" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="M7" s="92" t="n">
+        <v>1.06581410364015e-14</v>
+      </c>
+      <c r="N7" s="92" t="n">
+        <v>510.3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SR. NO.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>INVOICE NO.</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>PARTY NAME</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>GST NO.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>NET AMOUNT</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>CGST</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>SGST</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>IGST</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>R/OFF</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>TOTAL AMOUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AUGUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SALA/26-27/143</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>08/08/2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SHREE ANSUYA LEATHER ARTS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>27AHMPP0142M1Z2</t>
+        </is>
+      </c>
+      <c r="F3" s="92" t="n">
+        <v>5814.75</v>
+      </c>
+      <c r="H3" s="92" t="n">
+        <v>238.63</v>
+      </c>
+      <c r="J3" s="92" t="n">
+        <v>238.63</v>
+      </c>
+      <c r="M3" s="92" t="n">
+        <v>-0.009999999999990905</v>
+      </c>
+      <c r="N3" s="92" t="n">
+        <v>6292</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>26-27/00442</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AMIT HARDWARE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>27AXQPA4425N1Z4</t>
+        </is>
+      </c>
+      <c r="F4" s="92" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H4" s="92" t="n">
+        <v>720</v>
+      </c>
+      <c r="J4" s="92" t="n">
+        <v>720</v>
+      </c>
+      <c r="N4" s="92" t="n">
+        <v>9440</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>26-27/00470</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AMIT HARDWARE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>27AXQPA4425N1Z4</t>
+        </is>
+      </c>
+      <c r="F5" s="92" t="n">
+        <v>19450</v>
+      </c>
+      <c r="H5" s="92" t="n">
+        <v>1750.5</v>
+      </c>
+      <c r="J5" s="92" t="n">
+        <v>1750.5</v>
+      </c>
+      <c r="N5" s="92" t="n">
+        <v>22951</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CRN364441664721</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Porter</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>27AAGCR8772D1Z2</t>
+        </is>
+      </c>
+      <c r="F6" s="92" t="n">
+        <v>486</v>
+      </c>
+      <c r="H6" s="92" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="J6" s="92" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="M6" s="92" t="n">
+        <v>1.06581410364015e-14</v>
+      </c>
+      <c r="N6" s="92" t="n">
+        <v>510.3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CRN364441664721</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Porter</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>27AAGCR8772D1Z2</t>
+        </is>
+      </c>
+      <c r="F7" s="92" t="n">
+        <v>486</v>
+      </c>
+      <c r="L7" s="92" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="M7" s="92" t="n">
+        <v>1.06581410364015e-14</v>
+      </c>
+      <c r="N7" s="92" t="n">
+        <v>510.3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SR. NO.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>INVOICE NO.</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>PARTY NAME</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>GST NO.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>NET AMOUNT</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>CGST</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>SGST</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>IGST</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>R/OFF</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>TOTAL AMOUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AUGUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SALA/26-27/143</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>08/08/2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SHREE ANSUYA LEATHER ARTS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>27AHMPP0142M1Z2</t>
+        </is>
+      </c>
+      <c r="F3" s="92" t="n">
+        <v>5814.75</v>
+      </c>
+      <c r="H3" s="92" t="n">
+        <v>238.63</v>
+      </c>
+      <c r="J3" s="92" t="n">
+        <v>238.63</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" s="92" t="n">
+        <v>-0.009999999999990905</v>
+      </c>
+      <c r="N3" s="92" t="n">
+        <v>6292</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>26-27/00442</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AMIT HARDWARE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>27AXQPA4425N1Z4</t>
+        </is>
+      </c>
+      <c r="F4" s="92" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H4" s="92" t="n">
+        <v>720</v>
+      </c>
+      <c r="J4" s="92" t="n">
+        <v>720</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" s="92" t="n">
+        <v>9440</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>26-27/00470</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AMIT HARDWARE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>27AXQPA4425N1Z4</t>
+        </is>
+      </c>
+      <c r="F5" s="92" t="n">
+        <v>19450</v>
+      </c>
+      <c r="H5" s="92" t="n">
+        <v>1750.5</v>
+      </c>
+      <c r="J5" s="92" t="n">
+        <v>1750.5</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" s="92" t="n">
+        <v>22951</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CRN364441664721</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Porter</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>27AAGCR8772D1Z2</t>
+        </is>
+      </c>
+      <c r="F6" s="92" t="n">
+        <v>486</v>
+      </c>
+      <c r="H6" s="92" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="J6" s="92" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" s="92" t="n">
+        <v>1.06581410364015e-14</v>
+      </c>
+      <c r="N6" s="92" t="n">
+        <v>510.3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CRN364441664721</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Porter</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>27AAGCR8772D1Z2</t>
+        </is>
+      </c>
+      <c r="F7" s="92" t="n">
+        <v>486</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="L7" s="92" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="M7" s="92" t="n">
+        <v>1.06581410364015e-14</v>
+      </c>
+      <c r="N7" s="92" t="n">
+        <v>510.3</v>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2440,7 +3274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2552,7 +3386,6 @@
       <c r="J3" s="92" t="n">
         <v>238.63</v>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" s="92" t="n">
         <v>-0.009999999999990905</v>
       </c>
@@ -2590,7 +3423,6 @@
       <c r="J4" s="92" t="n">
         <v>720</v>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" s="92" t="n">
         <v>9440</v>
       </c>
@@ -2625,7 +3457,6 @@
       <c r="J5" s="92" t="n">
         <v>1750.5</v>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" s="92" t="n">
         <v>22951</v>
       </c>
@@ -2660,7 +3491,6 @@
       <c r="J6" s="92" t="n">
         <v>12.15</v>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" s="92" t="n">
         <v>1.06581410364015e-14</v>
       </c>
@@ -2692,8 +3522,6 @@
       <c r="F7" s="92" t="n">
         <v>486</v>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="L7" s="92" t="n">
         <v>24.3</v>
       </c>
@@ -2704,13 +3532,553 @@
         <v>510.3</v>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
+    <col width="5" customWidth="1" min="11" max="11"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SR. NO.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>INVOICE NO.</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>PARTY NAME</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>GST NO.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>NET AMOUNT</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>CGST</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>SGST</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>IGST</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>R/OFF</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>TOTAL AMOUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AUGUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SALA/26-27/143</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>08/08/2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SHREE ANSUYA LEATHER ARTS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>27AHMPP0142M1Z2</t>
+        </is>
+      </c>
+      <c r="F3" s="92" t="n">
+        <v>5814.75</v>
+      </c>
+      <c r="H3" s="92" t="n">
+        <v>238.63</v>
+      </c>
+      <c r="J3" s="92" t="n">
+        <v>238.63</v>
+      </c>
+      <c r="M3" s="92" t="n">
+        <v>-0.009999999999990905</v>
+      </c>
+      <c r="N3" s="92" t="n">
+        <v>6292</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>26-27/00442</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AMIT HARDWARE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>27AXQPA4425N1Z4</t>
+        </is>
+      </c>
+      <c r="F4" s="92" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H4" s="92" t="n">
+        <v>720</v>
+      </c>
+      <c r="J4" s="92" t="n">
+        <v>720</v>
+      </c>
+      <c r="N4" s="92" t="n">
+        <v>9440</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>26-27/00470</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AMIT HARDWARE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>27AXQPA4425N1Z4</t>
+        </is>
+      </c>
+      <c r="F5" s="92" t="n">
+        <v>19450</v>
+      </c>
+      <c r="H5" s="92" t="n">
+        <v>1750.5</v>
+      </c>
+      <c r="J5" s="92" t="n">
+        <v>1750.5</v>
+      </c>
+      <c r="N5" s="92" t="n">
+        <v>22951</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CRN364441664721</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Porter</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>27AAGCR8772D1Z2</t>
+        </is>
+      </c>
+      <c r="F6" s="92" t="n">
+        <v>486</v>
+      </c>
+      <c r="H6" s="92" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="J6" s="92" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="M6" s="92" t="n">
+        <v>1.06581410364015e-14</v>
+      </c>
+      <c r="N6" s="92" t="n">
+        <v>510.3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CRN364441664721</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Porter</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>27AAGCR8772D1Z2</t>
+        </is>
+      </c>
+      <c r="F7" s="92" t="n">
+        <v>486</v>
+      </c>
+      <c r="L7" s="92" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="M7" s="92" t="n">
+        <v>1.06581410364015e-14</v>
+      </c>
+      <c r="N7" s="92" t="n">
+        <v>510.3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SR. NO.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>INVOICE NO.</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>PARTY NAME</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>GST NO.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>NET AMOUNT</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>CGST</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>SGST</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>IGST</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>R/OFF</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>TOTAL AMOUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AUGUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SALA/26-27/143</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>08/08/2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SHREE ANSUYA LEATHER ARTS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>27AHMPP0142M1Z2</t>
+        </is>
+      </c>
+      <c r="F3" s="92" t="n">
+        <v>5814.75</v>
+      </c>
+      <c r="H3" s="92" t="n">
+        <v>238.63</v>
+      </c>
+      <c r="J3" s="92" t="n">
+        <v>238.63</v>
+      </c>
+      <c r="M3" s="92" t="n">
+        <v>-0.009999999999990905</v>
+      </c>
+      <c r="N3" s="92" t="n">
+        <v>6292</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>26-27/00442</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AMIT HARDWARE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>27AXQPA4425N1Z4</t>
+        </is>
+      </c>
+      <c r="F4" s="92" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H4" s="92" t="n">
+        <v>720</v>
+      </c>
+      <c r="J4" s="92" t="n">
+        <v>720</v>
+      </c>
+      <c r="N4" s="92" t="n">
+        <v>9440</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>26-27/00470</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AMIT HARDWARE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>27AXQPA4425N1Z4</t>
+        </is>
+      </c>
+      <c r="F5" s="92" t="n">
+        <v>19450</v>
+      </c>
+      <c r="H5" s="92" t="n">
+        <v>1750.5</v>
+      </c>
+      <c r="J5" s="92" t="n">
+        <v>1750.5</v>
+      </c>
+      <c r="N5" s="92" t="n">
+        <v>22951</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CRN364441664721</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Porter</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>27AAGCR8772D1Z2</t>
+        </is>
+      </c>
+      <c r="F6" s="92" t="n">
+        <v>486</v>
+      </c>
+      <c r="H6" s="92" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="J6" s="92" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="M6" s="92" t="n">
+        <v>1.06581410364015e-14</v>
+      </c>
+      <c r="N6" s="92" t="n">
+        <v>510.3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CRN364441664721</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Porter</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>27AAGCR8772D1Z2</t>
+        </is>
+      </c>
+      <c r="F7" s="92" t="n">
+        <v>486</v>
+      </c>
+      <c r="L7" s="92" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="M7" s="92" t="n">
+        <v>1.06581410364015e-14</v>
+      </c>
+      <c r="N7" s="92" t="n">
+        <v>510.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
